--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -19497,7 +19497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 20:53:30</t>
+          <t>2026-10-01 21:18:35</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>aa2b944</t>
+          <t>49adde6</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -19497,7 +19497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:18:35</t>
+          <t>2026-10-01 22:59:51</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>49adde6</t>
+          <t>e04913e</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 22:59:51</t>
+          <t>2026-10-02 10:31:41</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>e04913e</t>
+          <t>80489b0</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -2263,23 +2263,31 @@
           <t>05-037</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2435,23 +2443,31 @@
           <t>05-041</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2554,23 +2570,31 @@
           <t>05-044</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2591,23 +2615,31 @@
           <t>05-045</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr"/>
-      <c r="K49" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2628,23 +2660,31 @@
           <t>05-046</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr"/>
-      <c r="K50" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -4168,7 +4208,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4191,23 +4231,31 @@
           <t>05-085</t>
         </is>
       </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -4273,23 +4321,31 @@
           <t>05-087</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr"/>
-      <c r="K91" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -4310,23 +4366,31 @@
           <t>05-088</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr"/>
-      <c r="K92" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4347,23 +4411,31 @@
           <t>05-089</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -4384,23 +4456,31 @@
           <t>05-090</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -6335,23 +6415,31 @@
           <t>05-137</t>
         </is>
       </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="inlineStr"/>
-      <c r="K141" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -6417,23 +6505,31 @@
           <t>05-139</t>
         </is>
       </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H143" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J143" s="7" t="inlineStr"/>
-      <c r="K143" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -10012,23 +10108,31 @@
           <t>05-037</t>
         </is>
       </c>
-      <c r="P38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr"/>
-      <c r="T38" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="T38" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -10356,23 +10460,31 @@
           <t>05-041</t>
         </is>
       </c>
-      <c r="P42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr"/>
-      <c r="T42" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="T42" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -10604,23 +10716,31 @@
           <t>05-044</t>
         </is>
       </c>
-      <c r="P45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="T45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -10684,23 +10804,31 @@
           <t>05-045</t>
         </is>
       </c>
-      <c r="P46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr"/>
-      <c r="T46" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -10764,23 +10892,31 @@
           <t>05-046</t>
         </is>
       </c>
-      <c r="P47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr"/>
-      <c r="T47" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
+      <c r="T47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -13938,7 +14074,7 @@
       </c>
       <c r="T85" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -14004,23 +14140,31 @@
           <t>05-085</t>
         </is>
       </c>
-      <c r="P86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S86" s="7" t="inlineStr"/>
-      <c r="T86" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T86" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -14172,23 +14316,31 @@
           <t>05-087</t>
         </is>
       </c>
-      <c r="P88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S88" s="7" t="inlineStr"/>
-      <c r="T88" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T88" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -14252,23 +14404,31 @@
           <t>05-088</t>
         </is>
       </c>
-      <c r="P89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S89" s="7" t="inlineStr"/>
-      <c r="T89" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T89" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -14332,23 +14492,31 @@
           <t>05-089</t>
         </is>
       </c>
-      <c r="P90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S90" s="7" t="inlineStr"/>
-      <c r="T90" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -14412,23 +14580,31 @@
           <t>05-090</t>
         </is>
       </c>
-      <c r="P91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S91" s="7" t="inlineStr"/>
-      <c r="T91" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T91" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -18384,23 +18560,31 @@
           <t>05-137</t>
         </is>
       </c>
-      <c r="P138" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q138" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P138" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q138" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S138" s="7" t="inlineStr"/>
-      <c r="T138" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S138" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T138" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -18552,23 +18736,31 @@
           <t>05-139</t>
         </is>
       </c>
-      <c r="P140" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q140" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P140" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q140" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S140" s="7" t="inlineStr"/>
-      <c r="T140" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S140" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
+      <c r="T140" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -19497,7 +19689,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:31:41</t>
+          <t>2026-10-02 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80489b0</t>
+          <t>e20d5f2</t>
         </is>
       </c>
     </row>
@@ -20963,22 +21155,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -21107,22 +21303,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -21210,22 +21410,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -21243,22 +21447,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -21276,22 +21484,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/recovery_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -21897,22 +22109,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -21967,22 +22183,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -22000,22 +22220,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -22033,22 +22257,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -22066,22 +22294,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -22165,22 +22397,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -22235,22 +22471,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/handshake_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -19689,7 +19689,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:41:41</t>
+          <t>2026-10-02 10:43:55</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>e20d5f2</t>
+          <t>153705e</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -19689,7 +19689,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:43:55</t>
+          <t>2026-10-02 10:47:50</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>153705e</t>
+          <t>c955892</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -2488,23 +2488,31 @@
           <t>05-042</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr"/>
-      <c r="K46" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -4253,7 +4261,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6378,23 +6386,31 @@
           <t>05-136</t>
         </is>
       </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H140" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J140" s="7" t="inlineStr"/>
-      <c r="K140" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -6550,23 +6566,31 @@
           <t>05-140</t>
         </is>
       </c>
-      <c r="G144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J144" s="7" t="inlineStr"/>
-      <c r="K144" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -6661,23 +6685,31 @@
           <t>05-143</t>
         </is>
       </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H147" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J147" s="7" t="inlineStr"/>
-      <c r="K147" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -10548,23 +10580,31 @@
           <t>05-042</t>
         </is>
       </c>
-      <c r="P43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr"/>
-      <c r="T43" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T43" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -14162,7 +14202,7 @@
       </c>
       <c r="T86" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -18480,23 +18520,31 @@
           <t>05-136</t>
         </is>
       </c>
-      <c r="P137" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q137" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P137" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q137" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S137" s="7" t="inlineStr"/>
-      <c r="T137" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S137" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T137" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -18824,23 +18872,31 @@
           <t>05-140</t>
         </is>
       </c>
-      <c r="P141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S141" s="7" t="inlineStr"/>
-      <c r="T141" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S141" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T141" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -19064,23 +19120,31 @@
           <t>05-143</t>
         </is>
       </c>
-      <c r="P144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S144" s="7" t="inlineStr"/>
-      <c r="T144" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S144" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T144" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -19689,7 +19753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:47:50</t>
+          <t>2026-10-02 11:47:39</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c955892</t>
+          <t>14aeca4</t>
         </is>
       </c>
     </row>
@@ -21340,22 +21404,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -22364,22 +22432,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -22508,22 +22580,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -22607,22 +22683,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -19753,7 +19753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 11:47:39</t>
+          <t>2026-10-02 12:00:31</t>
         </is>
       </c>
     </row>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14aeca4</t>
+          <t>5168869</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/05_Mini_QUIC_ULTIMATE_145_Master_STATUS.xlsx
@@ -1641,23 +1641,31 @@
           <t>05-023</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3208,23 +3216,31 @@
           <t>05-058</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr"/>
-      <c r="K62" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3245,23 +3261,31 @@
           <t>05-059</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3282,23 +3306,31 @@
           <t>05-060</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -3319,23 +3351,31 @@
           <t>05-061</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3356,23 +3396,31 @@
           <t>05-062</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3393,23 +3441,31 @@
           <t>05-063</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3430,23 +3486,31 @@
           <t>05-064</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3467,23 +3531,31 @@
           <t>05-065</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3504,23 +3576,31 @@
           <t>05-066</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3541,23 +3621,31 @@
           <t>05-067</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr"/>
-      <c r="K71" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3578,23 +3666,31 @@
           <t>05-068</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -3615,23 +3711,31 @@
           <t>05-069</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr"/>
-      <c r="K73" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -3689,23 +3793,31 @@
           <t>05-071</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3726,23 +3838,31 @@
           <t>05-072</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3948,23 +4068,31 @@
           <t>05-078</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3985,23 +4113,31 @@
           <t>05-079</t>
         </is>
       </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="inlineStr"/>
-      <c r="K83" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -4022,23 +4158,31 @@
           <t>05-080</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -6349,23 +6493,31 @@
           <t>05-135</t>
         </is>
       </c>
-      <c r="G139" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H139" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="inlineStr"/>
-      <c r="K139" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/packet_codec_tests.rs</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -6408,7 +6560,7 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6859,7 @@
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -8916,23 +9068,31 @@
           <t>05-023</t>
         </is>
       </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr"/>
-      <c r="T24" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -11988,23 +12148,31 @@
           <t>05-058</t>
         </is>
       </c>
-      <c r="P59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr"/>
-      <c r="T59" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T59" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -12068,23 +12236,31 @@
           <t>05-059</t>
         </is>
       </c>
-      <c r="P60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr"/>
-      <c r="T60" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T60" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -12148,23 +12324,31 @@
           <t>05-060</t>
         </is>
       </c>
-      <c r="P61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr"/>
-      <c r="T61" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T61" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -12228,23 +12412,31 @@
           <t>05-061</t>
         </is>
       </c>
-      <c r="P62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr"/>
-      <c r="T62" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T62" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -12308,23 +12500,31 @@
           <t>05-062</t>
         </is>
       </c>
-      <c r="P63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr"/>
-      <c r="T63" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -12388,23 +12588,31 @@
           <t>05-063</t>
         </is>
       </c>
-      <c r="P64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr"/>
-      <c r="T64" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -12468,23 +12676,31 @@
           <t>05-064</t>
         </is>
       </c>
-      <c r="P65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S65" s="7" t="inlineStr"/>
-      <c r="T65" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T65" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -12548,23 +12764,31 @@
           <t>05-065</t>
         </is>
       </c>
-      <c r="P66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S66" s="7" t="inlineStr"/>
-      <c r="T66" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T66" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -12628,23 +12852,31 @@
           <t>05-066</t>
         </is>
       </c>
-      <c r="P67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr"/>
-      <c r="T67" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T67" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -12708,23 +12940,31 @@
           <t>05-067</t>
         </is>
       </c>
-      <c r="P68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S68" s="7" t="inlineStr"/>
-      <c r="T68" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T68" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -12788,23 +13028,31 @@
           <t>05-068</t>
         </is>
       </c>
-      <c r="P69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S69" s="7" t="inlineStr"/>
-      <c r="T69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T69" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -12868,23 +13116,31 @@
           <t>05-069</t>
         </is>
       </c>
-      <c r="P70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S70" s="7" t="inlineStr"/>
-      <c r="T70" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T70" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -13028,23 +13284,31 @@
           <t>05-071</t>
         </is>
       </c>
-      <c r="P72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S72" s="7" t="inlineStr"/>
-      <c r="T72" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T72" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -13108,23 +13372,31 @@
           <t>05-072</t>
         </is>
       </c>
-      <c r="P73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S73" s="7" t="inlineStr"/>
-      <c r="T73" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T73" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -13588,23 +13860,31 @@
           <t>05-078</t>
         </is>
       </c>
-      <c r="P79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S79" s="7" t="inlineStr"/>
-      <c r="T79" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -13668,23 +13948,31 @@
           <t>05-079</t>
         </is>
       </c>
-      <c r="P80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S80" s="7" t="inlineStr"/>
-      <c r="T80" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/path_simulator_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T80" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -13748,23 +14036,31 @@
           <t>05-080</t>
         </is>
       </c>
-      <c r="P81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S81" s="7" t="inlineStr"/>
-      <c r="T81" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
+      <c r="T81" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -18440,23 +18736,31 @@
           <t>05-135</t>
         </is>
       </c>
-      <c r="P136" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q136" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P136" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q136" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S136" s="7" t="inlineStr"/>
-      <c r="T136" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S136" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/packet_codec_tests.rs</t>
+        </is>
+      </c>
+      <c r="T136" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -18542,7 +18846,7 @@
       </c>
       <c r="T137" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19446,7 @@
       </c>
       <c r="T144" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -19753,7 +20057,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:00:31</t>
+          <t>2026-10-02 20:05:03</t>
         </is>
       </c>
     </row>
@@ -19765,7 +20069,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5168869</t>
+          <t>2700149</t>
         </is>
       </c>
     </row>
@@ -20705,22 +21009,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -21996,22 +22304,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/protocol_p0_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -22399,22 +22711,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>projects/05-mini-quic/backend/tests/packet_codec_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
